--- a/data/trans_orig/PCS12_SP_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170209</t>
+          <t>171982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214363</t>
+          <t>214669</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131657</t>
+          <t>131320</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167986</t>
+          <t>165400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308590</t>
+          <t>313385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>367237</t>
+          <t>367317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259413</t>
+          <t>259107</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303567</t>
+          <t>301794</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138694</t>
+          <t>141280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175023</t>
+          <t>175360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>413220</t>
+          <t>413140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>471867</t>
+          <t>467072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125924</t>
+          <t>127160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164462</t>
+          <t>165312</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134202</t>
+          <t>132870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169625</t>
+          <t>172977</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>269148</t>
+          <t>269715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323278</t>
+          <t>321556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202472</t>
+          <t>201622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>239774</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202240</t>
+          <t>198888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237663</t>
+          <t>238995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415521</t>
+          <t>417243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>469651</t>
+          <t>469084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>215290</t>
+          <t>214276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>261443</t>
+          <t>258246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80075</t>
+          <t>80659</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106478</t>
+          <t>107577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>305619</t>
+          <t>305282</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>359103</t>
+          <t>357787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280946</t>
+          <t>284143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327099</t>
+          <t>328113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61304</t>
+          <t>60205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87707</t>
+          <t>87123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351068</t>
+          <t>352384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>404552</t>
+          <t>404889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>559255</t>
+          <t>560304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>629104</t>
+          <t>630059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>360815</t>
+          <t>359646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>413619</t>
+          <t>414093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935653</t>
+          <t>937149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1021173</t>
+          <t>1025809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609230</t>
+          <t>608275</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>679079</t>
+          <t>678030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353470</t>
+          <t>354639</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>931447</t>
+          <t>926811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1016967</t>
+          <t>1015471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154516</t>
+          <t>154591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191451</t>
+          <t>193034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>307996</t>
+          <t>310945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>355245</t>
+          <t>357316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>473541</t>
+          <t>474256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>535868</t>
+          <t>535028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159104</t>
+          <t>157521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196039</t>
+          <t>195964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>213507</t>
+          <t>211436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>260756</t>
+          <t>257807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383439</t>
+          <t>384279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>445766</t>
+          <t>445051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40505</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67487</t>
+          <t>67453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>782610</t>
+          <t>779739</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>848892</t>
+          <t>845004</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>828506</t>
+          <t>829746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>901141</t>
+          <t>905247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230714</t>
+          <t>230748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257696</t>
+          <t>257390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>399868</t>
+          <t>403756</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>466150</t>
+          <t>469021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>645819</t>
+          <t>641713</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>718454</t>
+          <t>717214</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1339546</t>
+          <t>1333166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1448996</t>
+          <t>1446918</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1869654</t>
+          <t>1867456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1983498</t>
+          <t>1983039</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3235053</t>
+          <t>3236790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3397116</t>
+          <t>3397505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1821194</t>
+          <t>1823272</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1930644</t>
+          <t>1937024</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1394626</t>
+          <t>1395085</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1508470</t>
+          <t>1510668</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3251198</t>
+          <t>3250809</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3413261</t>
+          <t>3411524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135850</t>
+          <t>136804</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179220</t>
+          <t>179861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116796</t>
+          <t>116468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152611</t>
+          <t>153109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266871</t>
+          <t>266538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>322208</t>
+          <t>320558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257991</t>
+          <t>257350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301361</t>
+          <t>300407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161843</t>
+          <t>161345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197658</t>
+          <t>197986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>429457</t>
+          <t>431107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484794</t>
+          <t>485127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,54%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164244</t>
+          <t>165124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>206664</t>
+          <t>211740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119186</t>
+          <t>119435</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157936</t>
+          <t>157867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>296632</t>
+          <t>295729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>353755</t>
+          <t>355579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,98%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212133</t>
+          <t>207057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>254553</t>
+          <t>253673</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>180144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>218825</t>
+          <t>218576</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>403053</t>
+          <t>401229</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>460176</t>
+          <t>461079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,92%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>286132</t>
+          <t>289643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>338417</t>
+          <t>342099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129451</t>
+          <t>128524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161380</t>
+          <t>160877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>429811</t>
+          <t>427605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>490011</t>
+          <t>488505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>290998</t>
+          <t>287316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343283</t>
+          <t>339772</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98749</t>
+          <t>99252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130678</t>
+          <t>131605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>399533</t>
+          <t>401039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>459733</t>
+          <t>461939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>514792</t>
+          <t>510854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>582217</t>
+          <t>584660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>340489</t>
+          <t>339233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>394245</t>
+          <t>394345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>869864</t>
+          <t>871347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>962959</t>
+          <t>963809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>576792</t>
+          <t>574349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644217</t>
+          <t>648155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372412</t>
+          <t>372312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>426168</t>
+          <t>427424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>962708</t>
+          <t>961858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1055803</t>
+          <t>1054320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>214768</t>
+          <t>217860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>262156</t>
+          <t>260603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>446455</t>
+          <t>447438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>503481</t>
+          <t>500570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>679306</t>
+          <t>675073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>749965</t>
+          <t>748814</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,86%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>248440</t>
+          <t>249993</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>295828</t>
+          <t>292736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>258041</t>
+          <t>260952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>315067</t>
+          <t>314084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>522153</t>
+          <t>523304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>592812</t>
+          <t>597045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,93%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50296</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78200</t>
+          <t>78787</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>630307</t>
+          <t>630292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>699577</t>
+          <t>696580</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>692635</t>
+          <t>695603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>768737</t>
+          <t>765175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188682</t>
+          <t>188095</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216586</t>
+          <t>216923</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>409774</t>
+          <t>412771</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>479044</t>
+          <t>479059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>607496</t>
+          <t>611058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>683598</t>
+          <t>680630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1450721</t>
+          <t>1447413</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1565787</t>
+          <t>1566864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1864369</t>
+          <t>1859988</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1985926</t>
+          <t>1984006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3345325</t>
+          <t>3343100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3514254</t>
+          <t>3518116</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,46%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1856123</t>
+          <t>1855046</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1971189</t>
+          <t>1974497</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1564199</t>
+          <t>1566119</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1685756</t>
+          <t>1690137</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3457781</t>
+          <t>3453919</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3626710</t>
+          <t>3628935</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,05%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130064</t>
+          <t>129566</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168757</t>
+          <t>168502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97630</t>
+          <t>97716</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133829</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237351</t>
+          <t>236710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>292699</t>
+          <t>291077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260335</t>
+          <t>260590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>299028</t>
+          <t>299526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213226</t>
+          <t>214180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249425</t>
+          <t>249339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>483448</t>
+          <t>485070</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>538796</t>
+          <t>539437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106164</t>
+          <t>105999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143617</t>
+          <t>143478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120619</t>
+          <t>120656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>158653</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>236195</t>
+          <t>234474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>290579</t>
+          <t>288248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>233610</t>
+          <t>233749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>271063</t>
+          <t>271228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>213620</t>
+          <t>212493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251654</t>
+          <t>251617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>458921</t>
+          <t>461252</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>513305</t>
+          <t>515026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>205817</t>
+          <t>205117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>250113</t>
+          <t>251260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64496</t>
+          <t>67020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92175</t>
+          <t>92979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>281030</t>
+          <t>280689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>334317</t>
+          <t>332277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,29%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271801</t>
+          <t>270654</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316097</t>
+          <t>316797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73948</t>
+          <t>73144</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101627</t>
+          <t>99103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>353719</t>
+          <t>355759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>407006</t>
+          <t>407347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,2%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>466369</t>
+          <t>464139</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>534723</t>
+          <t>532680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>337961</t>
+          <t>336495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>394216</t>
+          <t>395549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>821299</t>
+          <t>818216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>904698</t>
+          <t>905166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614915</t>
+          <t>616958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>683269</t>
+          <t>685499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>431660</t>
+          <t>430327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>487915</t>
+          <t>489381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1070816</t>
+          <t>1070348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1154215</t>
+          <t>1157298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,58%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>234627</t>
+          <t>236258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>284147</t>
+          <t>286575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>378490</t>
+          <t>379425</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>433873</t>
+          <t>434241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>626690</t>
+          <t>630032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>703936</t>
+          <t>704354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336559</t>
+          <t>334131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>386079</t>
+          <t>384448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>304371</t>
+          <t>304003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>359754</t>
+          <t>358819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>655014</t>
+          <t>654596</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>732260</t>
+          <t>728918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47763</t>
+          <t>47628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74702</t>
+          <t>76151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>545533</t>
+          <t>548892</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>614289</t>
+          <t>617164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>604920</t>
+          <t>605234</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>679991</t>
+          <t>680483</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212443</t>
+          <t>210994</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239382</t>
+          <t>239517</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>467736</t>
+          <t>464861</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>536492</t>
+          <t>533133</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>689179</t>
+          <t>688687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>764250</t>
+          <t>763936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1264994</t>
+          <t>1264804</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1380422</t>
+          <t>1375769</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1622413</t>
+          <t>1624911</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1743788</t>
+          <t>1749141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2935637</t>
+          <t>2924978</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3093909</t>
+          <t>3090987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2005300</t>
+          <t>2009953</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2120728</t>
+          <t>2120918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1787808</t>
+          <t>1782455</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1909183</t>
+          <t>1906685</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3823409</t>
+          <t>3826331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3981681</t>
+          <t>3992340</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>207865</t>
+          <t>206855</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254230</t>
+          <t>253541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>175704</t>
+          <t>175836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210166</t>
+          <t>210377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>395680</t>
+          <t>395063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451097</t>
+          <t>451719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248820</t>
+          <t>249509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295185</t>
+          <t>296195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236010</t>
+          <t>235799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270472</t>
+          <t>270340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>498129</t>
+          <t>497507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553546</t>
+          <t>554163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172376</t>
+          <t>174119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216850</t>
+          <t>216709</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>156159</t>
+          <t>156032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188768</t>
+          <t>188957</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>337956</t>
+          <t>341536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390754</t>
+          <t>395373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234632</t>
+          <t>234773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>279106</t>
+          <t>277363</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193238</t>
+          <t>193049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>225847</t>
+          <t>225974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442733</t>
+          <t>438114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495531</t>
+          <t>491951</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,02%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>315024</t>
+          <t>313458</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>589071</t>
+          <t>582420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85776</t>
+          <t>86492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106979</t>
+          <t>106330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>419156</t>
+          <t>419056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>710633</t>
+          <t>705891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76297</t>
+          <t>82948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>350344</t>
+          <t>351910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58942</t>
+          <t>59591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80145</t>
+          <t>79429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120656</t>
+          <t>125398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>412133</t>
+          <t>412233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>460698</t>
+          <t>463519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>532228</t>
+          <t>532415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>496064</t>
+          <t>501873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>783755</t>
+          <t>783371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>986802</t>
+          <t>989790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1374217</t>
+          <t>1416338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497492</t>
+          <t>497305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>569022</t>
+          <t>566201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192071</t>
+          <t>192455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>479762</t>
+          <t>473953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>631330</t>
+          <t>589209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1018745</t>
+          <t>1015757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>226926</t>
+          <t>227433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>275284</t>
+          <t>272873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>330681</t>
+          <t>348371</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>515924</t>
+          <t>526828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>593184</t>
+          <t>571351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>774211</t>
+          <t>771029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195163</t>
+          <t>197574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243521</t>
+          <t>243014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>320731</t>
+          <t>309827</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>505974</t>
+          <t>488284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>532890</t>
+          <t>536072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>713917</t>
+          <t>735750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33261</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75273</t>
+          <t>73425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>400290</t>
+          <t>399301</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>452388</t>
+          <t>453217</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>440718</t>
+          <t>442574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>516104</t>
+          <t>513487</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,7%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165234</t>
+          <t>167082</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207246</t>
+          <t>207582</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300232</t>
+          <t>299403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>352330</t>
+          <t>353319</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>477023</t>
+          <t>479640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>552409</t>
+          <t>550553</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1523793</t>
+          <t>1521905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2098511</t>
+          <t>2095734</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1813807</t>
+          <t>1816313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2281169</t>
+          <t>2255467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3387666</t>
+          <t>3406847</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4009899</t>
+          <t>4093778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1262063</t>
+          <t>1264840</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1836781</t>
+          <t>1838669</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1278035</t>
+          <t>1303737</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1745397</t>
+          <t>1742891</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2909879</t>
+          <t>2826000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3532112</t>
+          <t>3512931</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>171982</t>
+          <t>170616</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214669</t>
+          <t>212360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131320</t>
+          <t>130400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165400</t>
+          <t>166479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>313385</t>
+          <t>313146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>367317</t>
+          <t>367429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259107</t>
+          <t>261416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301794</t>
+          <t>303160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141280</t>
+          <t>140201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175360</t>
+          <t>176280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>413140</t>
+          <t>413028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>467072</t>
+          <t>467311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>127160</t>
+          <t>125946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165312</t>
+          <t>163450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132870</t>
+          <t>132474</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172977</t>
+          <t>171626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>269715</t>
+          <t>267359</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321556</t>
+          <t>320896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201622</t>
+          <t>203484</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>239774</t>
+          <t>240988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>198888</t>
+          <t>200239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238995</t>
+          <t>239391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>417243</t>
+          <t>417903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>469084</t>
+          <t>471440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214276</t>
+          <t>215704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>258246</t>
+          <t>260857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80659</t>
+          <t>81724</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107577</t>
+          <t>107579</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>305282</t>
+          <t>305539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>357787</t>
+          <t>358104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284143</t>
+          <t>281532</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328113</t>
+          <t>326685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60205</t>
+          <t>60203</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>86058</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>352384</t>
+          <t>352067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>404889</t>
+          <t>404632</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>560304</t>
+          <t>555295</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>630059</t>
+          <t>623755</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>359646</t>
+          <t>359208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>414093</t>
+          <t>412251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>937149</t>
+          <t>933116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1025809</t>
+          <t>1025549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>608275</t>
+          <t>614579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>678030</t>
+          <t>683039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300192</t>
+          <t>302034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354639</t>
+          <t>355077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>926811</t>
+          <t>927071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015471</t>
+          <t>1019504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154591</t>
+          <t>154083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193034</t>
+          <t>193368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>310945</t>
+          <t>308322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>357316</t>
+          <t>356554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>474256</t>
+          <t>476126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>535028</t>
+          <t>537362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157521</t>
+          <t>157187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195964</t>
+          <t>196472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211436</t>
+          <t>212198</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>257807</t>
+          <t>260430</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384279</t>
+          <t>381945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>445051</t>
+          <t>443181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40811</t>
+          <t>39842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67453</t>
+          <t>66672</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>779739</t>
+          <t>783703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>845004</t>
+          <t>845671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>829746</t>
+          <t>824904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>905247</t>
+          <t>901545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230748</t>
+          <t>231529</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257390</t>
+          <t>258359</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>403756</t>
+          <t>403089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>469021</t>
+          <t>465057</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>641713</t>
+          <t>645415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>717214</t>
+          <t>722056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1333166</t>
+          <t>1332327</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1446918</t>
+          <t>1447040</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1867456</t>
+          <t>1863067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1983039</t>
+          <t>1982543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3236790</t>
+          <t>3230199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3397505</t>
+          <t>3398267</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1823272</t>
+          <t>1823150</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1937024</t>
+          <t>1937863</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1395085</t>
+          <t>1395581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1510668</t>
+          <t>1515057</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3250809</t>
+          <t>3250047</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3411524</t>
+          <t>3418115</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136804</t>
+          <t>138598</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179861</t>
+          <t>181123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116468</t>
+          <t>114762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153109</t>
+          <t>153358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266538</t>
+          <t>264186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>320558</t>
+          <t>320008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257350</t>
+          <t>256088</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300407</t>
+          <t>298613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161345</t>
+          <t>161096</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197986</t>
+          <t>199692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431107</t>
+          <t>431657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>485127</t>
+          <t>487479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,85%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>165124</t>
+          <t>166385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>211740</t>
+          <t>211535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119435</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157867</t>
+          <t>158529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>295729</t>
+          <t>295946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355579</t>
+          <t>355439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207057</t>
+          <t>207262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>253673</t>
+          <t>252412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180144</t>
+          <t>179482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>218576</t>
+          <t>218011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>401229</t>
+          <t>401369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>461079</t>
+          <t>460862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,9%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>289643</t>
+          <t>286826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342099</t>
+          <t>339784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128524</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160877</t>
+          <t>161236</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>427605</t>
+          <t>430718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>488505</t>
+          <t>494820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287316</t>
+          <t>289631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>339772</t>
+          <t>342589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99252</t>
+          <t>98893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131605</t>
+          <t>130559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>401039</t>
+          <t>394724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>461939</t>
+          <t>458826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>510854</t>
+          <t>512686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>584660</t>
+          <t>581963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>339233</t>
+          <t>338633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>394345</t>
+          <t>395833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>871347</t>
+          <t>872729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>963809</t>
+          <t>963338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,03%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>574349</t>
+          <t>577046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>648155</t>
+          <t>646323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372312</t>
+          <t>370824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>427424</t>
+          <t>428024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>961858</t>
+          <t>962329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1054320</t>
+          <t>1052938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>217860</t>
+          <t>214963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260603</t>
+          <t>260226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>447438</t>
+          <t>444332</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>500570</t>
+          <t>500271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>675073</t>
+          <t>676713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>748814</t>
+          <t>746823</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249993</t>
+          <t>250370</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>292736</t>
+          <t>295633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>260952</t>
+          <t>261251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>314084</t>
+          <t>317190</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>523304</t>
+          <t>525295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>597045</t>
+          <t>595405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>49208</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78787</t>
+          <t>77650</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>630292</t>
+          <t>631571</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>696580</t>
+          <t>700309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>695603</t>
+          <t>690455</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>765175</t>
+          <t>765056</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188095</t>
+          <t>189232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216923</t>
+          <t>217674</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>412771</t>
+          <t>409042</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>479059</t>
+          <t>477780</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>611058</t>
+          <t>611177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>680630</t>
+          <t>685778</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1447413</t>
+          <t>1443301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1566864</t>
+          <t>1564246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1859988</t>
+          <t>1867881</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1984006</t>
+          <t>1982584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3343100</t>
+          <t>3350054</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3518116</t>
+          <t>3526349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1855046</t>
+          <t>1857664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1974497</t>
+          <t>1978609</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1566119</t>
+          <t>1567541</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1690137</t>
+          <t>1682244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3453919</t>
+          <t>3445686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3628935</t>
+          <t>3621981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129566</t>
+          <t>129946</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168502</t>
+          <t>169634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97716</t>
+          <t>99062</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>134431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236710</t>
+          <t>239202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291077</t>
+          <t>292909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260590</t>
+          <t>259458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>299526</t>
+          <t>299146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214180</t>
+          <t>212624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249339</t>
+          <t>247993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485070</t>
+          <t>483238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539437</t>
+          <t>536945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105999</t>
+          <t>106610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143478</t>
+          <t>144934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120656</t>
+          <t>119693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159780</t>
+          <t>157703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>234474</t>
+          <t>235699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288248</t>
+          <t>291190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>233749</t>
+          <t>232293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>271228</t>
+          <t>270617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>212493</t>
+          <t>214570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251617</t>
+          <t>252580</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>461252</t>
+          <t>458310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>515026</t>
+          <t>513801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>205117</t>
+          <t>205819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>251260</t>
+          <t>252372</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67020</t>
+          <t>65183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92979</t>
+          <t>92265</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280689</t>
+          <t>279737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332277</t>
+          <t>333481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270654</t>
+          <t>269542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316797</t>
+          <t>316095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73144</t>
+          <t>73858</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99103</t>
+          <t>100940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355759</t>
+          <t>354555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>407347</t>
+          <t>408299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>464139</t>
+          <t>467194</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>532680</t>
+          <t>533010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>336495</t>
+          <t>336052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>395549</t>
+          <t>393797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>818216</t>
+          <t>821589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>905166</t>
+          <t>912509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616958</t>
+          <t>616628</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>685499</t>
+          <t>682444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>430327</t>
+          <t>432079</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>489381</t>
+          <t>489824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1070348</t>
+          <t>1063005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1157298</t>
+          <t>1153925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>236258</t>
+          <t>235569</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>286575</t>
+          <t>283507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>379425</t>
+          <t>379055</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>434241</t>
+          <t>433074</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>630032</t>
+          <t>629329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>704354</t>
+          <t>702718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>334131</t>
+          <t>337199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>384448</t>
+          <t>385137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>304003</t>
+          <t>305170</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>358819</t>
+          <t>359189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>654596</t>
+          <t>656232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>728918</t>
+          <t>729621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47628</t>
+          <t>47173</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76151</t>
+          <t>76249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>548892</t>
+          <t>546760</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>617164</t>
+          <t>612900</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>605234</t>
+          <t>604030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>680483</t>
+          <t>679764</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210994</t>
+          <t>210896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239517</t>
+          <t>239972</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>464861</t>
+          <t>469125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>533133</t>
+          <t>535265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>688687</t>
+          <t>689406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>763936</t>
+          <t>765140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1264804</t>
+          <t>1258379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1375769</t>
+          <t>1372338</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1624911</t>
+          <t>1628062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1749141</t>
+          <t>1747588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2924978</t>
+          <t>2919574</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3090987</t>
+          <t>3090131</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2009953</t>
+          <t>2013384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2120918</t>
+          <t>2127343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1782455</t>
+          <t>1784008</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1906685</t>
+          <t>1903534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3826331</t>
+          <t>3827187</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3992340</t>
+          <t>3997744</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>231058</t>
+          <t>251125</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>206855</t>
+          <t>228142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253541</t>
+          <t>276016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>192759</t>
+          <t>210504</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>175836</t>
+          <t>193785</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210377</t>
+          <t>228999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>423817</t>
+          <t>461629</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>395063</t>
+          <t>432172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451719</t>
+          <t>494670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>271992</t>
+          <t>297040</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249509</t>
+          <t>272149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296195</t>
+          <t>320023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>253417</t>
+          <t>276317</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235799</t>
+          <t>257822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270340</t>
+          <t>293036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>525409</t>
+          <t>573358</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497507</t>
+          <t>540317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554163</t>
+          <t>602815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503050</t>
+          <t>548165</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503050</t>
+          <t>548165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503050</t>
+          <t>548165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446176</t>
+          <t>486821</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446176</t>
+          <t>486821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446176</t>
+          <t>486821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>949226</t>
+          <t>1034987</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>949226</t>
+          <t>1034987</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>949226</t>
+          <t>1034987</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>193778</t>
+          <t>204876</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174119</t>
+          <t>183052</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216709</t>
+          <t>229263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>173400</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>156032</t>
+          <t>175937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188957</t>
+          <t>209861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>367177</t>
+          <t>398366</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>341536</t>
+          <t>370119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>395373</t>
+          <t>427891</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,3%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>257704</t>
+          <t>277332</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234773</t>
+          <t>252945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>277363</t>
+          <t>299156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>208606</t>
+          <t>228996</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193049</t>
+          <t>212625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>225974</t>
+          <t>246549</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>466310</t>
+          <t>506328</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>438114</t>
+          <t>476803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>491951</t>
+          <t>534575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451482</t>
+          <t>482208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451482</t>
+          <t>482208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451482</t>
+          <t>482208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>448995</t>
+          <t>221607</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>313458</t>
+          <t>199472</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>582420</t>
+          <t>244632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>96412</t>
+          <t>106766</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86492</t>
+          <t>95026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106330</t>
+          <t>118081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>545408</t>
+          <t>328374</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>419056</t>
+          <t>305044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>705891</t>
+          <t>354548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>216373</t>
+          <t>247061</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82948</t>
+          <t>224036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>351910</t>
+          <t>269196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69509</t>
+          <t>79683</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59591</t>
+          <t>68368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79429</t>
+          <t>91423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>285881</t>
+          <t>326744</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125398</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>412233</t>
+          <t>350074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>665368</t>
+          <t>468668</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>665368</t>
+          <t>468668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>665368</t>
+          <t>468668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165921</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165921</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165921</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>831289</t>
+          <t>655118</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>831289</t>
+          <t>655118</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>831289</t>
+          <t>655118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>498428</t>
+          <t>538307</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>463519</t>
+          <t>503070</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>532415</t>
+          <t>571554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>607664</t>
+          <t>446075</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>501873</t>
+          <t>418606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>783371</t>
+          <t>472157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1106093</t>
+          <t>984382</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>989790</t>
+          <t>939944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1416338</t>
+          <t>1030648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>51,92%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>531292</t>
+          <t>587973</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497305</t>
+          <t>554726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>566201</t>
+          <t>623210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>368162</t>
+          <t>412796</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192455</t>
+          <t>386714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473953</t>
+          <t>440265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>899454</t>
+          <t>1000769</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>589209</t>
+          <t>954503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015757</t>
+          <t>1045207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1029720</t>
+          <t>1126280</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1029720</t>
+          <t>1126280</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1029720</t>
+          <t>1126280</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975826</t>
+          <t>858871</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975826</t>
+          <t>858871</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975826</t>
+          <t>858871</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2005547</t>
+          <t>1985151</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2005547</t>
+          <t>1985151</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2005547</t>
+          <t>1985151</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>251572</t>
+          <t>291470</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>227433</t>
+          <t>265585</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>272873</t>
+          <t>319746</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>459500</t>
+          <t>502371</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348371</t>
+          <t>477877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>526828</t>
+          <t>524518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>711071</t>
+          <t>793841</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>571351</t>
+          <t>758399</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>771029</t>
+          <t>830071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>218875</t>
+          <t>271465</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197574</t>
+          <t>243189</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243014</t>
+          <t>297350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>377155</t>
+          <t>323586</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>309827</t>
+          <t>301439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>488284</t>
+          <t>348080</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>596030</t>
+          <t>595051</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>536072</t>
+          <t>558821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>735750</t>
+          <t>630493</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>470447</t>
+          <t>562935</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>470447</t>
+          <t>562935</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>470447</t>
+          <t>562935</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>836655</t>
+          <t>825957</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>836655</t>
+          <t>825957</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>836655</t>
+          <t>825957</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307101</t>
+          <t>1388892</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307101</t>
+          <t>1388892</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307101</t>
+          <t>1388892</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50381</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>32031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73425</t>
+          <t>69770</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>426451</t>
+          <t>462794</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>399301</t>
+          <t>433953</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>453217</t>
+          <t>492702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>476832</t>
+          <t>510395</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>442574</t>
+          <t>473194</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>513487</t>
+          <t>544163</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>190126</t>
+          <t>189628</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167082</t>
+          <t>167458</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207582</t>
+          <t>205197</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>326169</t>
+          <t>372390</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>299403</t>
+          <t>342482</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>353319</t>
+          <t>401231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>516295</t>
+          <t>562017</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479640</t>
+          <t>528249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>550553</t>
+          <t>599218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>752620</t>
+          <t>835184</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>752620</t>
+          <t>835184</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>752620</t>
+          <t>835184</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>993127</t>
+          <t>1072412</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>993127</t>
+          <t>1072412</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>993127</t>
+          <t>1072412</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1674213</t>
+          <t>1554986</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1521905</t>
+          <t>1493745</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2095734</t>
+          <t>1619516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1956186</t>
+          <t>1922000</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1816313</t>
+          <t>1866231</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2255467</t>
+          <t>1976780</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3630398</t>
+          <t>3476987</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3406847</t>
+          <t>3398979</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4093778</t>
+          <t>3560890</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1686361</t>
+          <t>1870498</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1264840</t>
+          <t>1805968</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1838669</t>
+          <t>1931739</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1603018</t>
+          <t>1693769</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1303737</t>
+          <t>1638989</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1742891</t>
+          <t>1749538</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3289380</t>
+          <t>3564266</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2826000</t>
+          <t>3480363</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3512931</t>
+          <t>3642274</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3360574</t>
+          <t>3425484</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3360574</t>
+          <t>3425484</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3360574</t>
+          <t>3425484</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3559204</t>
+          <t>3615769</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3559204</t>
+          <t>3615769</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3559204</t>
+          <t>3615769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6919778</t>
+          <t>7041253</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6919778</t>
+          <t>7041253</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6919778</t>
+          <t>7041253</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
